--- a/templates/excel/rechnungen-vorlage.xlsx
+++ b/templates/excel/rechnungen-vorlage.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="70">
   <si>
     <t>Rechnungen für easy-erechnung (ZUGFeRD / Factur-X EN16931, optional XRechnung)</t>
   </si>
@@ -23,7 +23,7 @@
     <t/>
   </si>
   <si>
-    <t>Blatt "Setup": eigene Daten (Name → Wert). Kleinunternehmer = ja → § 19 UStG, keine Umsatzsteuer.</t>
+    <t>Blatt "Setup": eigene Daten (Spalte A Bezeichnung, Spalte B Wert). Kleinunternehmer = ja → § 19 UStG, keine Umsatzsteuer.</t>
   </si>
   <si>
     <t>Blatt "Kunden": ein Kunde pro Zeile; im Rechnungsblatt wird er über das Kürzel ausgewählt.</t>
@@ -50,10 +50,13 @@
     <t>Fehlende Pflichtangaben führen zu einer Fehlermeldung mit Blatt und Zeile – es wird nichts ergänzt oder geraten.</t>
   </si>
   <si>
+    <t>Bezeichnung</t>
+  </si>
+  <si>
+    <t>Wert</t>
+  </si>
+  <si>
     <t>Name</t>
-  </si>
-  <si>
-    <t>Wert</t>
   </si>
   <si>
     <t>Max Mustermann</t>
@@ -383,109 +386,109 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="0"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" t="n" s="0">
         <v>19.0</v>
@@ -493,7 +496,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" t="n" s="0">
         <v>14.0</v>
@@ -501,10 +504,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -535,57 +538,57 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D1" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E1" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H1" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I1" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2" t="s" s="0">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" t="s" s="0">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" t="s" s="0">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I2" s="0"/>
     </row>
@@ -608,15 +611,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2" t="n" s="3">
         <v>46295.0</v>
@@ -624,29 +627,29 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="0"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6" t="n" s="3">
         <v>46266.0</v>
@@ -654,7 +657,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" t="n" s="3">
         <v>46295.0</v>
@@ -662,13 +665,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" s="0"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4" t="n">
         <f>SUMPRODUCT(D12:D200,E12:E200)</f>
@@ -677,19 +680,19 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12">
@@ -697,10 +700,10 @@
         <v>46267.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n" s="5">
         <v>1.5</v>
@@ -714,10 +717,10 @@
         <v>46274.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n" s="5">
         <v>1.5</v>
@@ -731,10 +734,10 @@
         <v>46281.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n" s="5">
         <v>2.0</v>
@@ -746,10 +749,10 @@
     <row r="15">
       <c r="A15" s="0"/>
       <c r="B15" t="s" s="0">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" t="n" s="5">
         <v>3.0</v>
